--- a/module-3/AssignmentDataFields.xlsx
+++ b/module-3/AssignmentDataFields.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bellevueuniversity-my.sharepoint.com/personal/mrodriguezgomez_my365_bellevue_edu/Documents/CSD/csd-310/module-3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{45210C2E-74E2-4CE7-85E5-A19509131D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26616609-6C7C-4A81-B1C0-F866BB6C875E}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{45210C2E-74E2-4CE7-85E5-A19509131D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{932CC4E8-BFCF-458C-A44F-1531EB9AD52E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{44D51683-A267-4CFA-94ED-6068418E5B14}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="61">
   <si>
     <t>M. Rodriguez Gomez</t>
   </si>
@@ -192,6 +192,33 @@
   </si>
   <si>
     <t>P-103</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>isbn</t>
+  </si>
+  <si>
+    <t>ID</t>
   </si>
 </sst>
 </file>
@@ -278,6 +305,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -791,16 +822,16 @@
     </row>
     <row r="10" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -852,22 +883,22 @@
     </row>
     <row r="16" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -937,7 +968,7 @@
     </row>
     <row r="22" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>2</v>
@@ -946,10 +977,10 @@
         <v>46</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
